--- a/Sales_Report.xlsx
+++ b/Sales_Report.xlsx
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>469.47</v>
+        <v>12966.8</v>
       </c>
     </row>
     <row r="3">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>125.8</v>
+        <v>1446.4</v>
       </c>
     </row>
     <row r="4">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>201.48</v>
+        <v>4023.92</v>
       </c>
     </row>
     <row r="5">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>426.27</v>
+        <v>22666.28</v>
       </c>
     </row>
     <row r="6">
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>110.16</v>
+        <v>1001.6</v>
       </c>
     </row>
     <row r="7">
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>80.14</v>
+        <v>1542.72</v>
       </c>
     </row>
     <row r="8">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>283.14</v>
+        <v>7175.7</v>
       </c>
     </row>
     <row r="9">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>364.47</v>
+        <v>2316.26</v>
       </c>
     </row>
     <row r="10">
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>295.75</v>
+        <v>14449.5</v>
       </c>
     </row>
     <row r="11">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>198.74</v>
+        <v>6779.700000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>232.14</v>
+        <v>11453.54</v>
       </c>
     </row>
     <row r="13">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>250.01</v>
+        <v>743.4699999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>258.73</v>
+        <v>8154.059999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>361.17</v>
+        <v>32567.58</v>
       </c>
     </row>
     <row r="16">
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>164.56</v>
+        <v>3083.08</v>
       </c>
     </row>
     <row r="17">
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>72.12</v>
+        <v>403.92</v>
       </c>
     </row>
     <row r="18">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>89.55</v>
+        <v>1554.3</v>
       </c>
     </row>
     <row r="19">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>114.65</v>
+        <v>1199.95</v>
       </c>
     </row>
     <row r="20">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>212.45</v>
+        <v>9701.700000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>324.66</v>
+        <v>4544.6</v>
       </c>
     </row>
     <row r="22">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>576.4</v>
+        <v>62667.4</v>
       </c>
     </row>
     <row r="23">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>266.43</v>
+        <v>14634.27</v>
       </c>
     </row>
     <row r="24">
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>417.16</v>
+        <v>18408.72</v>
       </c>
     </row>
     <row r="25">
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>69.89</v>
+        <v>1172.92</v>
       </c>
     </row>
     <row r="26">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>182.54</v>
+        <v>4395.16</v>
       </c>
     </row>
     <row r="27">
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>362.1</v>
+        <v>10294.1</v>
       </c>
     </row>
     <row r="28">
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>108.85</v>
+        <v>2955.45</v>
       </c>
     </row>
     <row r="29">
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>229.75</v>
+        <v>11962.5</v>
       </c>
     </row>
     <row r="30">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>203.2</v>
+        <v>4331.8</v>
       </c>
     </row>
     <row r="31">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>144.43</v>
+        <v>1397.62</v>
       </c>
     </row>
     <row r="32">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>68.15000000000001</v>
+        <v>324.45</v>
       </c>
     </row>
     <row r="33">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>269.39</v>
+        <v>3427.84</v>
       </c>
     </row>
     <row r="34">
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>101.29</v>
+        <v>1581.78</v>
       </c>
     </row>
     <row r="35">
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>529.21</v>
+        <v>19212.9</v>
       </c>
     </row>
     <row r="36">
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>100.19</v>
+        <v>2287.35</v>
       </c>
     </row>
     <row r="37">
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>324.08</v>
+        <v>2860.2</v>
       </c>
     </row>
     <row r="38">
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>140.54</v>
+        <v>2464.8</v>
       </c>
     </row>
     <row r="39">
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>242.28</v>
+        <v>1710.8</v>
       </c>
     </row>
     <row r="40">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>576.14</v>
+        <v>58357.3</v>
       </c>
     </row>
     <row r="41">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>281.81</v>
+        <v>19450.41</v>
       </c>
     </row>
     <row r="42">
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>330.59</v>
+        <v>4308.03</v>
       </c>
     </row>
     <row r="43">
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>498.2</v>
+        <v>4018</v>
       </c>
     </row>
     <row r="44">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>292.4</v>
+        <v>21336</v>
       </c>
     </row>
     <row r="45">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>130.86</v>
+        <v>490.22</v>
       </c>
     </row>
     <row r="46">
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>113.5</v>
+        <v>2422.5</v>
       </c>
     </row>
     <row r="47">
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>402.41</v>
+        <v>16211.37</v>
       </c>
     </row>
     <row r="48">
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>108.57</v>
+        <v>1838.97</v>
       </c>
     </row>
     <row r="49">
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>420.97</v>
+        <v>20737.08</v>
       </c>
     </row>
     <row r="50">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>365.72</v>
+        <v>3460.32</v>
       </c>
     </row>
     <row r="51">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>427.54</v>
+        <v>7972.32</v>
       </c>
     </row>
     <row r="52">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>363.6</v>
+        <v>7065.8</v>
       </c>
     </row>
     <row r="53">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>246.03</v>
+        <v>5334.66</v>
       </c>
     </row>
     <row r="54">
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>360.11</v>
+        <v>8100.96</v>
       </c>
     </row>
     <row r="55">
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>443.42</v>
+        <v>6599.76</v>
       </c>
     </row>
     <row r="56">
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>114.72</v>
+        <v>2289.08</v>
       </c>
     </row>
     <row r="57">
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>405.54</v>
+        <v>6805.52</v>
       </c>
     </row>
     <row r="58">
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>246.31</v>
+        <v>3963.99</v>
       </c>
     </row>
     <row r="59">
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>452.11</v>
+        <v>32346.93</v>
       </c>
     </row>
     <row r="60">
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>391.51</v>
+        <v>34063.11</v>
       </c>
     </row>
     <row r="61">
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>399.42</v>
+        <v>16257.32</v>
       </c>
     </row>
     <row r="62">
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>129.49</v>
+        <v>3246.66</v>
       </c>
     </row>
     <row r="63">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>285.95</v>
+        <v>6274.9</v>
       </c>
     </row>
     <row r="64">
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>113.66</v>
+        <v>2436.1</v>
       </c>
     </row>
     <row r="65">
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>65.66</v>
+        <v>904.36</v>
       </c>
     </row>
     <row r="66">
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="H66" s="2" t="n">
-        <v>337.69</v>
+        <v>8865.210000000001</v>
       </c>
     </row>
     <row r="67">
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="H67" s="2" t="n">
-        <v>244.66</v>
+        <v>7102.259999999999</v>
       </c>
     </row>
     <row r="68">
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="H68" s="2" t="n">
-        <v>136.03</v>
+        <v>658.9300000000001</v>
       </c>
     </row>
     <row r="69">
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="H69" s="2" t="n">
-        <v>345.95</v>
+        <v>7711.9</v>
       </c>
     </row>
     <row r="70">
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>307.02</v>
+        <v>3827.88</v>
       </c>
     </row>
     <row r="71">
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>113.06</v>
+        <v>442.54</v>
       </c>
     </row>
     <row r="72">
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="H72" s="2" t="n">
-        <v>170.94</v>
+        <v>5580.38</v>
       </c>
     </row>
     <row r="73">
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>373.35</v>
+        <v>8821.800000000001</v>
       </c>
     </row>
     <row r="74">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="H74" s="2" t="n">
-        <v>197.28</v>
+        <v>5192.48</v>
       </c>
     </row>
     <row r="75">
@@ -3292,7 +3292,7 @@
         </is>
       </c>
       <c r="H75" s="2" t="n">
-        <v>58.78</v>
+        <v>448.02</v>
       </c>
     </row>
     <row r="76">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="H76" s="2" t="n">
-        <v>132.58</v>
+        <v>4288.48</v>
       </c>
     </row>
     <row r="77">
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="H77" s="2" t="n">
-        <v>332.35</v>
+        <v>18044.4</v>
       </c>
     </row>
     <row r="78">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="H78" s="2" t="n">
-        <v>477.04</v>
+        <v>9594.24</v>
       </c>
     </row>
     <row r="79">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="H79" s="2" t="n">
-        <v>321.2</v>
+        <v>24676.8</v>
       </c>
     </row>
     <row r="80">
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="H80" s="2" t="n">
-        <v>451.08</v>
+        <v>8654.48</v>
       </c>
     </row>
     <row r="81">
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="H81" s="2" t="n">
-        <v>327.42</v>
+        <v>2995.56</v>
       </c>
     </row>
     <row r="82">
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="H82" s="2" t="n">
-        <v>70</v>
+        <v>549</v>
       </c>
     </row>
     <row r="83">
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="H83" s="2" t="n">
-        <v>171.55</v>
+        <v>2140.9</v>
       </c>
     </row>
     <row r="84">
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>503.67</v>
+        <v>9054.950000000001</v>
       </c>
     </row>
     <row r="85">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="H85" s="2" t="n">
-        <v>147.11</v>
+        <v>5319.04</v>
       </c>
     </row>
     <row r="86">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="H86" s="2" t="n">
-        <v>171.94</v>
+        <v>7386.96</v>
       </c>
     </row>
     <row r="87">
@@ -3724,7 +3724,7 @@
         </is>
       </c>
       <c r="H87" s="2" t="n">
-        <v>140.6</v>
+        <v>3203.2</v>
       </c>
     </row>
     <row r="88">
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="H88" s="2" t="n">
-        <v>391.46</v>
+        <v>12623.76</v>
       </c>
     </row>
     <row r="89">
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="H89" s="2" t="n">
-        <v>352.89</v>
+        <v>23641.07</v>
       </c>
     </row>
     <row r="90">
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="H90" s="2" t="n">
-        <v>66.18000000000001</v>
+        <v>737.36</v>
       </c>
     </row>
     <row r="91">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="H91" s="2" t="n">
-        <v>32.69</v>
+        <v>153.63</v>
       </c>
     </row>
     <row r="92">
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="H92" s="2" t="n">
-        <v>388.63</v>
+        <v>19075.53</v>
       </c>
     </row>
     <row r="93">
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="H93" s="2" t="n">
-        <v>423.76</v>
+        <v>15267.84</v>
       </c>
     </row>
     <row r="94">
@@ -3976,7 +3976,7 @@
         </is>
       </c>
       <c r="H94" s="2" t="n">
-        <v>311.01</v>
+        <v>5550.92</v>
       </c>
     </row>
     <row r="95">
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="H95" s="2" t="n">
-        <v>529.52</v>
+        <v>20261.76</v>
       </c>
     </row>
     <row r="96">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="H96" s="2" t="n">
-        <v>331.67</v>
+        <v>13538.28</v>
       </c>
     </row>
     <row r="97">
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="H97" s="2" t="n">
-        <v>328.12</v>
+        <v>7611.360000000001</v>
       </c>
     </row>
     <row r="98">
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="H98" s="2" t="n">
-        <v>194.03</v>
+        <v>8682.1</v>
       </c>
     </row>
     <row r="99">
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="H99" s="2" t="n">
-        <v>488.99</v>
+        <v>11155.35</v>
       </c>
     </row>
     <row r="100">
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="H100" s="2" t="n">
-        <v>471.4</v>
+        <v>2976</v>
       </c>
     </row>
     <row r="101">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="H101" s="2" t="n">
-        <v>408.41</v>
+        <v>21593.86</v>
       </c>
     </row>
     <row r="102">
@@ -4264,7 +4264,7 @@
         </is>
       </c>
       <c r="H102" s="2" t="n">
-        <v>654.11</v>
+        <v>90079.27</v>
       </c>
     </row>
     <row r="103">
@@ -4300,7 +4300,7 @@
         </is>
       </c>
       <c r="H103" s="2" t="n">
-        <v>395.71</v>
+        <v>2991.48</v>
       </c>
     </row>
     <row r="104">
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="H104" s="2" t="n">
-        <v>591.9300000000001</v>
+        <v>64783.71000000001</v>
       </c>
     </row>
     <row r="105">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="H105" s="2" t="n">
-        <v>465.9</v>
+        <v>4514.400000000001</v>
       </c>
     </row>
     <row r="106">
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="H106" s="2" t="n">
-        <v>538.36</v>
+        <v>59729.52</v>
       </c>
     </row>
     <row r="107">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H107" s="2" t="n">
-        <v>430.24</v>
+        <v>6324.6</v>
       </c>
     </row>
     <row r="108">
@@ -4480,7 +4480,7 @@
         </is>
       </c>
       <c r="H108" s="2" t="n">
-        <v>479.06</v>
+        <v>47666.46</v>
       </c>
     </row>
     <row r="109">
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="H109" s="2" t="n">
-        <v>216.59</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="110">
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>134.48</v>
+        <v>1944.64</v>
       </c>
     </row>
     <row r="111">
@@ -4588,7 +4588,7 @@
         </is>
       </c>
       <c r="H111" s="2" t="n">
-        <v>190.85</v>
+        <v>1260.4</v>
       </c>
     </row>
     <row r="112">
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>233.27</v>
+        <v>13598.13</v>
       </c>
     </row>
     <row r="113">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="H113" s="2" t="n">
-        <v>211.94</v>
+        <v>614.46</v>
       </c>
     </row>
     <row r="114">
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="H114" s="2" t="n">
-        <v>533.89</v>
+        <v>16945</v>
       </c>
     </row>
     <row r="115">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="H115" s="2" t="n">
-        <v>358.01</v>
+        <v>8328.33</v>
       </c>
     </row>
     <row r="116">
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="H116" s="2" t="n">
-        <v>203.22</v>
+        <v>5084.28</v>
       </c>
     </row>
     <row r="117">
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="H117" s="2" t="n">
-        <v>474.93</v>
+        <v>9502.219999999999</v>
       </c>
     </row>
     <row r="118">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="H118" s="2" t="n">
-        <v>312.45</v>
+        <v>3155.9</v>
       </c>
     </row>
     <row r="119">
@@ -4876,7 +4876,7 @@
         </is>
       </c>
       <c r="H119" s="2" t="n">
-        <v>67.22999999999999</v>
+        <v>1037.52</v>
       </c>
     </row>
     <row r="120">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="H120" s="2" t="n">
-        <v>242.36</v>
+        <v>11106.16</v>
       </c>
     </row>
     <row r="121">
@@ -4948,7 +4948,7 @@
         </is>
       </c>
       <c r="H121" s="2" t="n">
-        <v>240.12</v>
+        <v>2763.36</v>
       </c>
     </row>
     <row r="122">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="H122" s="2" t="n">
-        <v>514.98</v>
+        <v>26096.84</v>
       </c>
     </row>
     <row r="123">
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="H123" s="2" t="n">
-        <v>116.26</v>
+        <v>1365.78</v>
       </c>
     </row>
     <row r="124">
@@ -5056,7 +5056,7 @@
         </is>
       </c>
       <c r="H124" s="2" t="n">
-        <v>356.61</v>
+        <v>4668.23</v>
       </c>
     </row>
     <row r="125">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="H125" s="2" t="n">
-        <v>241.74</v>
+        <v>8853.300000000001</v>
       </c>
     </row>
     <row r="126">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="H126" s="2" t="n">
-        <v>247.88</v>
+        <v>9727.120000000001</v>
       </c>
     </row>
     <row r="127">
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="H127" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>433.84</v>
       </c>
     </row>
     <row r="128">
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="H128" s="2" t="n">
-        <v>359.71</v>
+        <v>4075.08</v>
       </c>
     </row>
     <row r="129">
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="H129" s="2" t="n">
-        <v>437.61</v>
+        <v>38428.76</v>
       </c>
     </row>
     <row r="130">
@@ -5272,7 +5272,7 @@
         </is>
       </c>
       <c r="H130" s="2" t="n">
-        <v>475.44</v>
+        <v>36832.32</v>
       </c>
     </row>
     <row r="131">
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c r="H131" s="2" t="n">
-        <v>217.55</v>
+        <v>3691.45</v>
       </c>
     </row>
     <row r="132">
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="H132" s="2" t="n">
-        <v>152.64</v>
+        <v>4169.88</v>
       </c>
     </row>
     <row r="133">
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="H133" s="2" t="n">
-        <v>168.44</v>
+        <v>5665.679999999999</v>
       </c>
     </row>
     <row r="134">
@@ -5416,7 +5416,7 @@
         </is>
       </c>
       <c r="H134" s="2" t="n">
-        <v>244.18</v>
+        <v>7177.8</v>
       </c>
     </row>
     <row r="135">
@@ -5452,7 +5452,7 @@
         </is>
       </c>
       <c r="H135" s="2" t="n">
-        <v>485.57</v>
+        <v>6405.04</v>
       </c>
     </row>
     <row r="136">
@@ -5488,7 +5488,7 @@
         </is>
       </c>
       <c r="H136" s="2" t="n">
-        <v>194.23</v>
+        <v>9178.99</v>
       </c>
     </row>
     <row r="137">
@@ -5524,7 +5524,7 @@
         </is>
       </c>
       <c r="H137" s="2" t="n">
-        <v>477.82</v>
+        <v>9514.74</v>
       </c>
     </row>
     <row r="138">
@@ -5560,7 +5560,7 @@
         </is>
       </c>
       <c r="H138" s="2" t="n">
-        <v>121.93</v>
+        <v>3426.54</v>
       </c>
     </row>
     <row r="139">
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="H139" s="2" t="n">
-        <v>393.03</v>
+        <v>2713.58</v>
       </c>
     </row>
     <row r="140">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="H140" s="2" t="n">
-        <v>402.12</v>
+        <v>5851.44</v>
       </c>
     </row>
     <row r="141">
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="H141" s="2" t="n">
-        <v>337.2</v>
+        <v>26793.8</v>
       </c>
     </row>
     <row r="142">
@@ -5704,7 +5704,7 @@
         </is>
       </c>
       <c r="H142" s="2" t="n">
-        <v>271.49</v>
+        <v>1719.85</v>
       </c>
     </row>
     <row r="143">
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="H143" s="2" t="n">
-        <v>467.09</v>
+        <v>9830.049999999999</v>
       </c>
     </row>
     <row r="144">
@@ -5776,7 +5776,7 @@
         </is>
       </c>
       <c r="H144" s="2" t="n">
-        <v>438.5</v>
+        <v>11685</v>
       </c>
     </row>
     <row r="145">
@@ -5812,7 +5812,7 @@
         </is>
       </c>
       <c r="H145" s="2" t="n">
-        <v>40.94</v>
+        <v>145.78</v>
       </c>
     </row>
     <row r="146">
@@ -5848,7 +5848,7 @@
         </is>
       </c>
       <c r="H146" s="2" t="n">
-        <v>264.05</v>
+        <v>4892.2</v>
       </c>
     </row>
     <row r="147">
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="H147" s="2" t="n">
-        <v>451.26</v>
+        <v>2785.7</v>
       </c>
     </row>
     <row r="148">
@@ -5920,7 +5920,7 @@
         </is>
       </c>
       <c r="H148" s="2" t="n">
-        <v>374.76</v>
+        <v>7349.040000000001</v>
       </c>
     </row>
     <row r="149">
@@ -5956,7 +5956,7 @@
         </is>
       </c>
       <c r="H149" s="2" t="n">
-        <v>416.24</v>
+        <v>7259.52</v>
       </c>
     </row>
     <row r="150">
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="H150" s="2" t="n">
-        <v>157.97</v>
+        <v>460.35</v>
       </c>
     </row>
     <row r="151">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="H151" s="2" t="n">
-        <v>47.8</v>
+        <v>250.8</v>
       </c>
     </row>
     <row r="152">
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="H152" s="2" t="n">
-        <v>283.57</v>
+        <v>5890.77</v>
       </c>
     </row>
     <row r="153">
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="H153" s="2" t="n">
-        <v>481.6</v>
+        <v>4531.2</v>
       </c>
     </row>
     <row r="154">
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="H154" s="2" t="n">
-        <v>465.41</v>
+        <v>13228.35</v>
       </c>
     </row>
     <row r="155">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="H155" s="2" t="n">
-        <v>114.68</v>
+        <v>920.0799999999999</v>
       </c>
     </row>
     <row r="156">
@@ -6208,7 +6208,7 @@
         </is>
       </c>
       <c r="H156" s="2" t="n">
-        <v>333.26</v>
+        <v>14685.06</v>
       </c>
     </row>
     <row r="157">
@@ -6244,7 +6244,7 @@
         </is>
       </c>
       <c r="H157" s="2" t="n">
-        <v>807.51</v>
+        <v>157942.25</v>
       </c>
     </row>
     <row r="158">
@@ -6280,7 +6280,7 @@
         </is>
       </c>
       <c r="H158" s="2" t="n">
-        <v>278.79</v>
+        <v>6066.45</v>
       </c>
     </row>
     <row r="159">
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="H159" s="2" t="n">
-        <v>527.39</v>
+        <v>33319.06</v>
       </c>
     </row>
     <row r="160">
@@ -6352,7 +6352,7 @@
         </is>
       </c>
       <c r="H160" s="2" t="n">
-        <v>251.24</v>
+        <v>15778.48</v>
       </c>
     </row>
     <row r="161">
@@ -6388,7 +6388,7 @@
         </is>
       </c>
       <c r="H161" s="2" t="n">
-        <v>505.27</v>
+        <v>7956.03</v>
       </c>
     </row>
     <row r="162">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H162" s="2" t="n">
-        <v>448.78</v>
+        <v>11301.16</v>
       </c>
     </row>
     <row r="163">
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="H163" s="2" t="n">
-        <v>454.74</v>
+        <v>22922.78</v>
       </c>
     </row>
     <row r="164">
@@ -6496,7 +6496,7 @@
         </is>
       </c>
       <c r="H164" s="2" t="n">
-        <v>522.15</v>
+        <v>16210.35</v>
       </c>
     </row>
     <row r="165">
@@ -6532,7 +6532,7 @@
         </is>
       </c>
       <c r="H165" s="2" t="n">
-        <v>306.11</v>
+        <v>8555.25</v>
       </c>
     </row>
     <row r="166">
@@ -6568,7 +6568,7 @@
         </is>
       </c>
       <c r="H166" s="2" t="n">
-        <v>505.76</v>
+        <v>3864.48</v>
       </c>
     </row>
     <row r="167">
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="H167" s="2" t="n">
-        <v>483.06</v>
+        <v>35995.46</v>
       </c>
     </row>
     <row r="168">
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="H168" s="2" t="n">
-        <v>409.24</v>
+        <v>14518.8</v>
       </c>
     </row>
     <row r="169">
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="H169" s="2" t="n">
-        <v>384.98</v>
+        <v>35719.42</v>
       </c>
     </row>
     <row r="170">
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="H170" s="2" t="n">
-        <v>95.23</v>
+        <v>1929.18</v>
       </c>
     </row>
     <row r="171">
@@ -6748,7 +6748,7 @@
         </is>
       </c>
       <c r="H171" s="2" t="n">
-        <v>187.51</v>
+        <v>1692.78</v>
       </c>
     </row>
     <row r="172">
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="H172" s="2" t="n">
-        <v>147.21</v>
+        <v>3075.62</v>
       </c>
     </row>
     <row r="173">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H173" s="2" t="n">
-        <v>66.51000000000001</v>
+        <v>1045.91</v>
       </c>
     </row>
     <row r="174">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="H174" s="2" t="n">
-        <v>265.5</v>
+        <v>17507</v>
       </c>
     </row>
     <row r="175">
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="H175" s="2" t="n">
-        <v>523.63</v>
+        <v>34990.35</v>
       </c>
     </row>
     <row r="176">
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="H176" s="2" t="n">
-        <v>141.64</v>
+        <v>1970.64</v>
       </c>
     </row>
     <row r="177">
@@ -6964,7 +6964,7 @@
         </is>
       </c>
       <c r="H177" s="2" t="n">
-        <v>179.24</v>
+        <v>7437.36</v>
       </c>
     </row>
     <row r="178">
@@ -7000,7 +7000,7 @@
         </is>
       </c>
       <c r="H178" s="2" t="n">
-        <v>322.93</v>
+        <v>6879</v>
       </c>
     </row>
     <row r="179">
@@ -7036,7 +7036,7 @@
         </is>
       </c>
       <c r="H179" s="2" t="n">
-        <v>477.43</v>
+        <v>24841.74</v>
       </c>
     </row>
     <row r="180">
@@ -7072,7 +7072,7 @@
         </is>
       </c>
       <c r="H180" s="2" t="n">
-        <v>145.42</v>
+        <v>4936.68</v>
       </c>
     </row>
     <row r="181">
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="H181" s="2" t="n">
-        <v>245.77</v>
+        <v>5474.17</v>
       </c>
     </row>
     <row r="182">
@@ -7144,7 +7144,7 @@
         </is>
       </c>
       <c r="H182" s="2" t="n">
-        <v>230.11</v>
+        <v>12016.5</v>
       </c>
     </row>
     <row r="183">
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="H183" s="2" t="n">
-        <v>189.42</v>
+        <v>2361.92</v>
       </c>
     </row>
     <row r="184">
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="H184" s="2" t="n">
-        <v>365.67</v>
+        <v>5817.830000000001</v>
       </c>
     </row>
     <row r="185">
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="H185" s="2" t="n">
-        <v>89.51000000000001</v>
+        <v>760.8</v>
       </c>
     </row>
     <row r="186">
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="H186" s="2" t="n">
-        <v>308.66</v>
+        <v>15043.68</v>
       </c>
     </row>
     <row r="187">
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="H187" s="2" t="n">
-        <v>260.79</v>
+        <v>5424.02</v>
       </c>
     </row>
     <row r="188">
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="H188" s="2" t="n">
-        <v>139.75</v>
+        <v>3718</v>
       </c>
     </row>
     <row r="189">
@@ -7396,7 +7396,7 @@
         </is>
       </c>
       <c r="H189" s="2" t="n">
-        <v>406.48</v>
+        <v>38307.84</v>
       </c>
     </row>
     <row r="190">
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="H190" s="2" t="n">
-        <v>431.68</v>
+        <v>31171.2</v>
       </c>
     </row>
     <row r="191">
@@ -7468,7 +7468,7 @@
         </is>
       </c>
       <c r="H191" s="2" t="n">
-        <v>482.39</v>
+        <v>31994.17</v>
       </c>
     </row>
     <row r="192">
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="H192" s="2" t="n">
-        <v>614.6900000000001</v>
+        <v>82655.03999999999</v>
       </c>
     </row>
     <row r="193">
@@ -7540,7 +7540,7 @@
         </is>
       </c>
       <c r="H193" s="2" t="n">
-        <v>257.27</v>
+        <v>3695.34</v>
       </c>
     </row>
     <row r="194">
@@ -7576,7 +7576,7 @@
         </is>
       </c>
       <c r="H194" s="2" t="n">
-        <v>494.69</v>
+        <v>9807.060000000001</v>
       </c>
     </row>
     <row r="195">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="H195" s="2" t="n">
-        <v>119.35</v>
+        <v>3383.55</v>
       </c>
     </row>
     <row r="196">
@@ -7648,7 +7648,7 @@
         </is>
       </c>
       <c r="H196" s="2" t="n">
-        <v>331.37</v>
+        <v>11747.67</v>
       </c>
     </row>
     <row r="197">
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="H197" s="2" t="n">
-        <v>343.78</v>
+        <v>8198.040000000001</v>
       </c>
     </row>
     <row r="198">
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="H198" s="2" t="n">
-        <v>238.49</v>
+        <v>3454.27</v>
       </c>
     </row>
     <row r="199">
@@ -7756,7 +7756,7 @@
         </is>
       </c>
       <c r="H199" s="2" t="n">
-        <v>256.9</v>
+        <v>5568.7</v>
       </c>
     </row>
     <row r="200">
@@ -7792,7 +7792,7 @@
         </is>
       </c>
       <c r="H200" s="2" t="n">
-        <v>241.33</v>
+        <v>1487.55</v>
       </c>
     </row>
     <row r="201">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="H201" s="2" t="n">
-        <v>457.29</v>
+        <v>9696.15</v>
       </c>
     </row>
     <row r="202">
@@ -7864,7 +7864,7 @@
         </is>
       </c>
       <c r="H202" s="2" t="n">
-        <v>303.62</v>
+        <v>12806.86</v>
       </c>
     </row>
     <row r="203">
@@ -7900,7 +7900,7 @@
         </is>
       </c>
       <c r="H203" s="2" t="n">
-        <v>268.3</v>
+        <v>8809</v>
       </c>
     </row>
     <row r="204">
@@ -7936,7 +7936,7 @@
         </is>
       </c>
       <c r="H204" s="2" t="n">
-        <v>157.24</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="205">
@@ -7972,7 +7972,7 @@
         </is>
       </c>
       <c r="H205" s="2" t="n">
-        <v>480.06</v>
+        <v>8343.719999999999</v>
       </c>
     </row>
     <row r="206">
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="H206" s="2" t="n">
-        <v>106.32</v>
+        <v>1994.24</v>
       </c>
     </row>
     <row r="207">
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="H207" s="2" t="n">
-        <v>393.19</v>
+        <v>9951.540000000001</v>
       </c>
     </row>
     <row r="208">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="H208" s="2" t="n">
-        <v>237.57</v>
+        <v>5233.41</v>
       </c>
     </row>
     <row r="209">
@@ -8116,7 +8116,7 @@
         </is>
       </c>
       <c r="H209" s="2" t="n">
-        <v>236.11</v>
+        <v>4146.87</v>
       </c>
     </row>
     <row r="210">
@@ -8152,7 +8152,7 @@
         </is>
       </c>
       <c r="H210" s="2" t="n">
-        <v>271.62</v>
+        <v>13794.48</v>
       </c>
     </row>
     <row r="211">
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="H211" s="2" t="n">
-        <v>524.67</v>
+        <v>17442.63</v>
       </c>
     </row>
     <row r="212">
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="H212" s="2" t="n">
-        <v>202.98</v>
+        <v>792.02</v>
       </c>
     </row>
     <row r="213">
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="H213" s="2" t="n">
-        <v>160.07</v>
+        <v>481.99</v>
       </c>
     </row>
     <row r="214">
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="H214" s="2" t="n">
-        <v>336.35</v>
+        <v>15778</v>
       </c>
     </row>
     <row r="215">
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="H215" s="2" t="n">
-        <v>423.08</v>
+        <v>3759.12</v>
       </c>
     </row>
     <row r="216">
@@ -8368,7 +8368,7 @@
         </is>
       </c>
       <c r="H216" s="2" t="n">
-        <v>278.29</v>
+        <v>6169.66</v>
       </c>
     </row>
     <row r="217">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="H217" s="2" t="n">
-        <v>279.67</v>
+        <v>6747.51</v>
       </c>
     </row>
     <row r="218">
@@ -8440,7 +8440,7 @@
         </is>
       </c>
       <c r="H218" s="2" t="n">
-        <v>366.33</v>
+        <v>6707.509999999999</v>
       </c>
     </row>
     <row r="219">
@@ -8476,7 +8476,7 @@
         </is>
       </c>
       <c r="H219" s="2" t="n">
-        <v>490.97</v>
+        <v>43488.75</v>
       </c>
     </row>
     <row r="220">
@@ -8512,7 +8512,7 @@
         </is>
       </c>
       <c r="H220" s="2" t="n">
-        <v>479.8</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="221">
@@ -8548,7 +8548,7 @@
         </is>
       </c>
       <c r="H221" s="2" t="n">
-        <v>306.57</v>
+        <v>7942.46</v>
       </c>
     </row>
     <row r="222">
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="H222" s="2" t="n">
-        <v>315.04</v>
+        <v>2168.32</v>
       </c>
     </row>
     <row r="223">
@@ -8620,7 +8620,7 @@
         </is>
       </c>
       <c r="H223" s="2" t="n">
-        <v>178.85</v>
+        <v>6196.95</v>
       </c>
     </row>
     <row r="224">
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="H224" s="2" t="n">
-        <v>477.88</v>
+        <v>13386.24</v>
       </c>
     </row>
     <row r="225">
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="H225" s="2" t="n">
-        <v>150.83</v>
+        <v>1770.54</v>
       </c>
     </row>
     <row r="226">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="H226" s="2" t="n">
-        <v>248.78</v>
+        <v>2791.86</v>
       </c>
     </row>
     <row r="227">
@@ -8764,7 +8764,7 @@
         </is>
       </c>
       <c r="H227" s="2" t="n">
-        <v>218.75</v>
+        <v>10547.25</v>
       </c>
     </row>
     <row r="228">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="H228" s="2" t="n">
-        <v>196</v>
+        <v>8308</v>
       </c>
     </row>
     <row r="229">
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="H229" s="2" t="n">
-        <v>24.24</v>
+        <v>143.36</v>
       </c>
     </row>
     <row r="230">
@@ -8872,7 +8872,7 @@
         </is>
       </c>
       <c r="H230" s="2" t="n">
-        <v>639.74</v>
+        <v>72688.08</v>
       </c>
     </row>
     <row r="231">
@@ -8908,7 +8908,7 @@
         </is>
       </c>
       <c r="H231" s="2" t="n">
-        <v>508.56</v>
+        <v>42242.24</v>
       </c>
     </row>
     <row r="232">
@@ -8944,7 +8944,7 @@
         </is>
       </c>
       <c r="H232" s="2" t="n">
-        <v>410.05</v>
+        <v>7448.55</v>
       </c>
     </row>
     <row r="233">
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="H233" s="2" t="n">
-        <v>115.26</v>
+        <v>883.8199999999999</v>
       </c>
     </row>
     <row r="234">
@@ -9016,7 +9016,7 @@
         </is>
       </c>
       <c r="H234" s="2" t="n">
-        <v>95.65000000000001</v>
+        <v>1049.95</v>
       </c>
     </row>
     <row r="235">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="H235" s="2" t="n">
-        <v>375.83</v>
+        <v>10004.01</v>
       </c>
     </row>
     <row r="236">
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="H236" s="2" t="n">
-        <v>293.99</v>
+        <v>12390.57</v>
       </c>
     </row>
     <row r="237">
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="H237" s="2" t="n">
-        <v>443.7</v>
+        <v>31833</v>
       </c>
     </row>
     <row r="238">
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="H238" s="2" t="n">
-        <v>449.43</v>
+        <v>18711.29</v>
       </c>
     </row>
     <row r="239">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="H239" s="2" t="n">
-        <v>66.04000000000001</v>
+        <v>362.4</v>
       </c>
     </row>
     <row r="240">
@@ -9232,7 +9232,7 @@
         </is>
       </c>
       <c r="H240" s="2" t="n">
-        <v>390.59</v>
+        <v>27385.41</v>
       </c>
     </row>
     <row r="241">
@@ -9268,7 +9268,7 @@
         </is>
       </c>
       <c r="H241" s="2" t="n">
-        <v>343.73</v>
+        <v>28231.84</v>
       </c>
     </row>
     <row r="242">
@@ -9304,7 +9304,7 @@
         </is>
       </c>
       <c r="H242" s="2" t="n">
-        <v>399.72</v>
+        <v>2253.68</v>
       </c>
     </row>
     <row r="243">
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="H243" s="2" t="n">
-        <v>304.29</v>
+        <v>5230.94</v>
       </c>
     </row>
     <row r="244">
@@ -9376,7 +9376,7 @@
         </is>
       </c>
       <c r="H244" s="2" t="n">
-        <v>280.89</v>
+        <v>11882.81</v>
       </c>
     </row>
     <row r="245">
@@ -9412,7 +9412,7 @@
         </is>
       </c>
       <c r="H245" s="2" t="n">
-        <v>80.33</v>
+        <v>893.11</v>
       </c>
     </row>
     <row r="246">
@@ -9448,7 +9448,7 @@
         </is>
       </c>
       <c r="H246" s="2" t="n">
-        <v>441.26</v>
+        <v>11285.64</v>
       </c>
     </row>
     <row r="247">
@@ -9484,7 +9484,7 @@
         </is>
       </c>
       <c r="H247" s="2" t="n">
-        <v>194.14</v>
+        <v>4942.96</v>
       </c>
     </row>
     <row r="248">
@@ -9520,7 +9520,7 @@
         </is>
       </c>
       <c r="H248" s="2" t="n">
-        <v>230.26</v>
+        <v>3676.38</v>
       </c>
     </row>
     <row r="249">
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="H249" s="2" t="n">
-        <v>335.01</v>
+        <v>22656.41</v>
       </c>
     </row>
     <row r="250">
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="H250" s="2" t="n">
-        <v>273.55</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="251">
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="H251" s="2" t="n">
-        <v>285.4</v>
+        <v>5406</v>
       </c>
     </row>
     <row r="252">
@@ -9664,7 +9664,7 @@
         </is>
       </c>
       <c r="H252" s="2" t="n">
-        <v>581.73</v>
+        <v>64683.35999999999</v>
       </c>
     </row>
     <row r="253">
@@ -9700,7 +9700,7 @@
         </is>
       </c>
       <c r="H253" s="2" t="n">
-        <v>153.88</v>
+        <v>3209.52</v>
       </c>
     </row>
     <row r="254">
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="H254" s="2" t="n">
-        <v>222.31</v>
+        <v>4283.309999999999</v>
       </c>
     </row>
     <row r="255">
@@ -9772,7 +9772,7 @@
         </is>
       </c>
       <c r="H255" s="2" t="n">
-        <v>290.61</v>
+        <v>6786.65</v>
       </c>
     </row>
     <row r="256">
@@ -9808,7 +9808,7 @@
         </is>
       </c>
       <c r="H256" s="2" t="n">
-        <v>571.4</v>
+        <v>55606.8</v>
       </c>
     </row>
     <row r="257">
@@ -9844,7 +9844,7 @@
         </is>
       </c>
       <c r="H257" s="2" t="n">
-        <v>182.12</v>
+        <v>558.48</v>
       </c>
     </row>
     <row r="258">
@@ -9880,7 +9880,7 @@
         </is>
       </c>
       <c r="H258" s="2" t="n">
-        <v>202.91</v>
+        <v>8729.309999999999</v>
       </c>
     </row>
     <row r="259">
@@ -9916,7 +9916,7 @@
         </is>
       </c>
       <c r="H259" s="2" t="n">
-        <v>405.39</v>
+        <v>11050.64</v>
       </c>
     </row>
     <row r="260">
@@ -9952,7 +9952,7 @@
         </is>
       </c>
       <c r="H260" s="2" t="n">
-        <v>335.64</v>
+        <v>10426.64</v>
       </c>
     </row>
     <row r="261">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="H261" s="2" t="n">
-        <v>459.57</v>
+        <v>5183.360000000001</v>
       </c>
     </row>
     <row r="262">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="H262" s="2" t="n">
-        <v>596.5699999999999</v>
+        <v>86831.64</v>
       </c>
     </row>
     <row r="263">
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="H263" s="2" t="n">
-        <v>430.14</v>
+        <v>13880.3</v>
       </c>
     </row>
     <row r="264">
@@ -10096,7 +10096,7 @@
         </is>
       </c>
       <c r="H264" s="2" t="n">
-        <v>497.71</v>
+        <v>7572.22</v>
       </c>
     </row>
     <row r="265">
@@ -10132,7 +10132,7 @@
         </is>
       </c>
       <c r="H265" s="2" t="n">
-        <v>488.59</v>
+        <v>45825.58</v>
       </c>
     </row>
     <row r="266">
@@ -10168,7 +10168,7 @@
         </is>
       </c>
       <c r="H266" s="2" t="n">
-        <v>152.99</v>
+        <v>3594.76</v>
       </c>
     </row>
     <row r="267">
@@ -10204,7 +10204,7 @@
         </is>
       </c>
       <c r="H267" s="2" t="n">
-        <v>33.37</v>
+        <v>171.99</v>
       </c>
     </row>
     <row r="268">
@@ -10240,7 +10240,7 @@
         </is>
       </c>
       <c r="H268" s="2" t="n">
-        <v>522.1900000000001</v>
+        <v>57165.54</v>
       </c>
     </row>
     <row r="269">
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="H269" s="2" t="n">
-        <v>249.19</v>
+        <v>9532.379999999999</v>
       </c>
     </row>
     <row r="270">
@@ -10312,7 +10312,7 @@
         </is>
       </c>
       <c r="H270" s="2" t="n">
-        <v>265.31</v>
+        <v>1885.98</v>
       </c>
     </row>
     <row r="271">
@@ -10348,7 +10348,7 @@
         </is>
       </c>
       <c r="H271" s="2" t="n">
-        <v>288.15</v>
+        <v>6851.299999999999</v>
       </c>
     </row>
     <row r="272">
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="H272" s="2" t="n">
-        <v>472.07</v>
+        <v>9931.5</v>
       </c>
     </row>
     <row r="273">
@@ -10420,7 +10420,7 @@
         </is>
       </c>
       <c r="H273" s="2" t="n">
-        <v>65.01000000000001</v>
+        <v>504.56</v>
       </c>
     </row>
     <row r="274">
@@ -10456,7 +10456,7 @@
         </is>
       </c>
       <c r="H274" s="2" t="n">
-        <v>16.08</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="275">
@@ -10492,7 +10492,7 @@
         </is>
       </c>
       <c r="H275" s="2" t="n">
-        <v>470.3</v>
+        <v>9135</v>
       </c>
     </row>
     <row r="276">
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="H276" s="2" t="n">
-        <v>82.87</v>
+        <v>1714.41</v>
       </c>
     </row>
     <row r="277">
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="H277" s="2" t="n">
-        <v>213.42</v>
+        <v>6304.76</v>
       </c>
     </row>
     <row r="278">
@@ -10600,7 +10600,7 @@
         </is>
       </c>
       <c r="H278" s="2" t="n">
-        <v>451.95</v>
+        <v>38738.15</v>
       </c>
     </row>
     <row r="279">
@@ -10636,7 +10636,7 @@
         </is>
       </c>
       <c r="H279" s="2" t="n">
-        <v>512.21</v>
+        <v>31403.61</v>
       </c>
     </row>
     <row r="280">
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="H280" s="2" t="n">
-        <v>212.58</v>
+        <v>2702.42</v>
       </c>
     </row>
     <row r="281">
@@ -10708,7 +10708,7 @@
         </is>
       </c>
       <c r="H281" s="2" t="n">
-        <v>461.03</v>
+        <v>4523.53</v>
       </c>
     </row>
     <row r="282">
@@ -10744,7 +10744,7 @@
         </is>
       </c>
       <c r="H282" s="2" t="n">
-        <v>137.34</v>
+        <v>3893.6</v>
       </c>
     </row>
     <row r="283">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="H283" s="2" t="n">
-        <v>202.96</v>
+        <v>9917.16</v>
       </c>
     </row>
     <row r="284">
@@ -10816,7 +10816,7 @@
         </is>
       </c>
       <c r="H284" s="2" t="n">
-        <v>249.94</v>
+        <v>10721.7</v>
       </c>
     </row>
     <row r="285">
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="H285" s="2" t="n">
-        <v>260.99</v>
+        <v>6725.679999999999</v>
       </c>
     </row>
     <row r="286">
@@ -10888,7 +10888,7 @@
         </is>
       </c>
       <c r="H286" s="2" t="n">
-        <v>486.05</v>
+        <v>8896.35</v>
       </c>
     </row>
     <row r="287">
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="H287" s="2" t="n">
-        <v>474.11</v>
+        <v>25589.32</v>
       </c>
     </row>
     <row r="288">
@@ -10960,7 +10960,7 @@
         </is>
       </c>
       <c r="H288" s="2" t="n">
-        <v>210.89</v>
+        <v>2918.44</v>
       </c>
     </row>
     <row r="289">
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="H289" s="2" t="n">
-        <v>292.84</v>
+        <v>4647.84</v>
       </c>
     </row>
     <row r="290">
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="H290" s="2" t="n">
-        <v>179.07</v>
+        <v>8010.44</v>
       </c>
     </row>
     <row r="291">
@@ -11068,7 +11068,7 @@
         </is>
       </c>
       <c r="H291" s="2" t="n">
-        <v>494.46</v>
+        <v>20007</v>
       </c>
     </row>
     <row r="292">
@@ -11104,7 +11104,7 @@
         </is>
       </c>
       <c r="H292" s="2" t="n">
-        <v>269.4</v>
+        <v>2693.6</v>
       </c>
     </row>
     <row r="293">
@@ -11140,7 +11140,7 @@
         </is>
       </c>
       <c r="H293" s="2" t="n">
-        <v>202.68</v>
+        <v>9800.640000000001</v>
       </c>
     </row>
     <row r="294">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="H294" s="2" t="n">
-        <v>279.01</v>
+        <v>9362.4</v>
       </c>
     </row>
     <row r="295">
@@ -11212,7 +11212,7 @@
         </is>
       </c>
       <c r="H295" s="2" t="n">
-        <v>526.8200000000001</v>
+        <v>28746.3</v>
       </c>
     </row>
     <row r="296">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="H296" s="2" t="n">
-        <v>401.22</v>
+        <v>17627.22</v>
       </c>
     </row>
     <row r="297">
@@ -11284,7 +11284,7 @@
         </is>
       </c>
       <c r="H297" s="2" t="n">
-        <v>288.44</v>
+        <v>13268.64</v>
       </c>
     </row>
     <row r="298">
@@ -11320,7 +11320,7 @@
         </is>
       </c>
       <c r="H298" s="2" t="n">
-        <v>163.06</v>
+        <v>799.4799999999999</v>
       </c>
     </row>
     <row r="299">
@@ -11356,7 +11356,7 @@
         </is>
       </c>
       <c r="H299" s="2" t="n">
-        <v>380.42</v>
+        <v>8026.360000000001</v>
       </c>
     </row>
     <row r="300">
@@ -11392,7 +11392,7 @@
         </is>
       </c>
       <c r="H300" s="2" t="n">
-        <v>114.39</v>
+        <v>889.34</v>
       </c>
     </row>
     <row r="301">
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="H301" s="2" t="n">
-        <v>83.33</v>
+        <v>1435.47</v>
       </c>
     </row>
   </sheetData>
@@ -11465,61 +11465,61 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9241</v>
+        <v>17011</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Home &amp; Office</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>12665</v>
+        <v>13372</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Stationery</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>17011</v>
+        <v>13068</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Fitness</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>10450</v>
+        <v>12665</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Home &amp; Office</t>
+          <t>Fitness</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>13372</v>
+        <v>10450</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Stationery</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>13068</v>
+        <v>9241</v>
       </c>
     </row>
   </sheetData>
